--- a/DataTables/Datas/#BuffInfo.xlsx
+++ b/DataTables/Datas/#BuffInfo.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -536,14 +536,6 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,17 +543,8 @@
           <t>##</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>Channeling</t>
@@ -577,7 +560,6 @@
           <t>正在引导 {T} 格，中途被打断则施法失败</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Neutral</t>
@@ -594,7 +576,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>Recoil</t>
@@ -610,7 +591,6 @@
           <t>僵直中，剩余 {T} 格无法行动</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Debuff</t>
@@ -627,7 +607,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>ReduceDmg</t>
@@ -664,7 +643,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>Chill</t>
@@ -701,7 +679,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>Stun</t>
@@ -738,7 +715,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>Vulnerable</t>
@@ -775,7 +751,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>ReduceChannel</t>
@@ -812,7 +787,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>Root</t>
@@ -849,7 +823,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>DrawCard</t>
@@ -886,7 +859,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>Taunt</t>
@@ -923,7 +895,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>Taunted</t>
@@ -960,7 +931,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>Stagger</t>
@@ -997,7 +967,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>Block</t>
@@ -1034,7 +1003,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>Strength</t>
@@ -1071,7 +1039,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>Weak</t>
@@ -1108,7 +1075,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>Frail</t>
@@ -1145,7 +1111,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>Dexterity</t>
@@ -1182,7 +1147,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>Regen</t>
@@ -1219,7 +1183,6 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>Energized</t>
@@ -1256,7 +1219,6 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>CardCost</t>
@@ -1293,7 +1255,6 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
           <t>Poison</t>
@@ -1330,7 +1291,6 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
           <t>Burn</t>
@@ -1367,7 +1327,6 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
           <t>Artifact</t>
@@ -1400,6 +1359,42 @@
         <v>99</v>
       </c>
       <c r="I27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Dodge</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>闪避</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>闪避下一次受到的攻击，剩余 {V} 次</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>UI/Buff/Icon_Dodge</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>99</v>
+      </c>
+      <c r="I28" t="b">
         <v>0</v>
       </c>
     </row>

--- a/DataTables/Datas/#BuffInfo.xlsx
+++ b/DataTables/Datas/#BuffInfo.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>禁锢</t>
+          <t>定身</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">

--- a/DataTables/Datas/#BuffInfo.xlsx
+++ b/DataTables/Datas/#BuffInfo.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1398,6 +1398,37 @@
         <v>0</v>
       </c>
     </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Resolve</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>坚毅</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>被打断后意志愈发坚定：每层使打断阈值提高 50%，当前 {V} 层</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>99</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DataTables/Datas/#BuffInfo.xlsx
+++ b/DataTables/Datas/#BuffInfo.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1429,6 +1429,42 @@
         <v>0</v>
       </c>
     </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Morale</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>士气</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>特殊增益，当前 {V} 层</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>UI/Buff/Icon_Morale</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
